--- a/DATA/base_tesis_mensual.xlsx
+++ b/DATA/base_tesis_mensual.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29421"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29509"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebasteitor\Desktop\MODELOS ECONOMETRICOS\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6B9922-D4B9-412A-9868-9F6EC4F109B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74107E3-78A6-4906-B3F4-886E5E5B8A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2970" yWindow="0" windowWidth="17055" windowHeight="15585" xr2:uid="{03477C2C-1FC9-4CA1-9345-B963C68C7E06}"/>
+    <workbookView xWindow="1560" yWindow="0" windowWidth="24840" windowHeight="15585" xr2:uid="{03477C2C-1FC9-4CA1-9345-B963C68C7E06}"/>
   </bookViews>
   <sheets>
     <sheet name="base_mensual" sheetId="1" r:id="rId1"/>
@@ -427,7 +427,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -437,7 +437,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -773,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834503D2-CD42-45E8-A68C-7EEDFF8EDF01}">
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="1"/>
@@ -800,7 +799,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="4">
@@ -2458,7 +2457,7 @@
       </c>
       <c r="G80" s="4"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>85</v>
       </c>
@@ -2479,7 +2478,7 @@
       </c>
       <c r="G81" s="4"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>86</v>
       </c>
@@ -2500,7 +2499,7 @@
       </c>
       <c r="G82" s="4"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>87</v>
       </c>
@@ -2521,7 +2520,7 @@
       </c>
       <c r="G83" s="4"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>88</v>
       </c>
@@ -2542,7 +2541,7 @@
       </c>
       <c r="G84" s="4"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>89</v>
       </c>
@@ -2563,7 +2562,7 @@
       </c>
       <c r="G85" s="4"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>90</v>
       </c>
@@ -2584,7 +2583,7 @@
       </c>
       <c r="G86" s="4"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>91</v>
       </c>
@@ -2605,7 +2604,7 @@
       </c>
       <c r="G87" s="4"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>92</v>
       </c>
@@ -2626,7 +2625,7 @@
       </c>
       <c r="G88" s="4"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>93</v>
       </c>
@@ -2647,11 +2646,8 @@
       </c>
       <c r="G89" s="4"/>
       <c r="I89" s="4"/>
-      <c r="K89">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -2671,11 +2667,8 @@
         <v>2.2191665250899772E-2</v>
       </c>
       <c r="G90" s="4"/>
-      <c r="K90">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>95</v>
       </c>
@@ -2695,12 +2688,8 @@
         <v>0.21431119560689593</v>
       </c>
       <c r="G91" s="4"/>
-      <c r="K91">
-        <f>K90-8</f>
-        <v>99</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>96</v>
       </c>
@@ -2721,7 +2710,7 @@
       </c>
       <c r="G92" s="4"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>97</v>
       </c>
@@ -2742,7 +2731,7 @@
       </c>
       <c r="G93" s="4"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>98</v>
       </c>
@@ -2763,7 +2752,7 @@
       </c>
       <c r="G94" s="4"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>99</v>
       </c>
@@ -2784,7 +2773,7 @@
       </c>
       <c r="G95" s="4"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>100</v>
       </c>
